--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -742,6 +742,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -751,7 +754,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -930,6 +933,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -973,7 +979,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1153,6 +1159,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1162,7 +1171,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1342,6 +1351,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16470742.053078819</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16842108.331714839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1384,7 +1396,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1564,6 +1576,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1573,7 +1588,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1753,6 +1768,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7109407.2353513949</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7480773.5139874145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1774,11 +1792,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99720192"/>
-        <c:axId val="103724160"/>
+        <c:axId val="494486656"/>
+        <c:axId val="494488960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99720192"/>
+        <c:axId val="494486656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1821,14 +1839,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103724160"/>
+        <c:crossAx val="494488960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103724160"/>
+        <c:axId val="494488960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1879,7 +1897,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99720192"/>
+        <c:crossAx val="494486656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2040,7 +2058,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2220,6 +2238,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-2500093.7589145182</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-10715332.987082755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2234,8 +2255,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="426328832"/>
-        <c:axId val="426322944"/>
+        <c:axId val="502073984"/>
+        <c:axId val="502072448"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2260,7 +2281,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2440,6 +2461,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2449,7 +2473,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2629,6 +2653,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2645,11 +2672,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426319872"/>
-        <c:axId val="426321408"/>
+        <c:axId val="502065024"/>
+        <c:axId val="502066560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426319872"/>
+        <c:axId val="502065024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2692,14 +2719,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426321408"/>
+        <c:crossAx val="502066560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426321408"/>
+        <c:axId val="502066560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2750,12 +2777,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426319872"/>
+        <c:crossAx val="502065024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="426322944"/>
+        <c:axId val="502072448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2792,12 +2819,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426328832"/>
+        <c:crossAx val="502073984"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="426328832"/>
+        <c:axId val="502073984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2806,7 +2833,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426322944"/>
+        <c:crossAx val="502072448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2938,7 +2965,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3118,6 +3145,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3132,8 +3162,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="424745216"/>
-        <c:axId val="399842304"/>
+        <c:axId val="620203008"/>
+        <c:axId val="620200704"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3158,7 +3188,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3338,6 +3368,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3347,7 +3380,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3527,6 +3560,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3543,11 +3579,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399531392"/>
-        <c:axId val="399840384"/>
+        <c:axId val="515625344"/>
+        <c:axId val="515626880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399531392"/>
+        <c:axId val="515625344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3590,14 +3626,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399840384"/>
+        <c:crossAx val="515626880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399840384"/>
+        <c:axId val="515626880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3648,12 +3684,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399531392"/>
+        <c:crossAx val="515625344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399842304"/>
+        <c:axId val="620200704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3690,12 +3726,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="424745216"/>
+        <c:crossAx val="620203008"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="424745216"/>
+        <c:axId val="620203008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3704,7 +3740,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399842304"/>
+        <c:crossAx val="620200704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3854,7 +3890,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4034,6 +4070,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4043,7 +4082,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4222,6 +4261,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4265,7 +4307,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4445,6 +4487,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4454,7 +4499,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4634,6 +4679,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17697629.703050636</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18094777.250086345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4676,7 +4724,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4856,6 +4904,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4865,7 +4916,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5045,6 +5096,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7689856.1635277644</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8087003.7105634734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5066,11 +5120,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="448737280"/>
-        <c:axId val="448739200"/>
+        <c:axId val="485796864"/>
+        <c:axId val="485798656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="448737280"/>
+        <c:axId val="485796864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5113,14 +5167,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448739200"/>
+        <c:crossAx val="485798656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448739200"/>
+        <c:axId val="485798656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5171,7 +5225,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448737280"/>
+        <c:crossAx val="485796864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5332,7 +5386,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5512,6 +5566,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-394977.32401696721</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-1098753.7286700674</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5526,8 +5583,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="605799168"/>
-        <c:axId val="559991424"/>
+        <c:axId val="492178816"/>
+        <c:axId val="492177280"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5552,7 +5609,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5732,6 +5789,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5741,7 +5801,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5921,6 +5981,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5937,11 +6000,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="524069888"/>
-        <c:axId val="559989504"/>
+        <c:axId val="485812864"/>
+        <c:axId val="492175744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="524069888"/>
+        <c:axId val="485812864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5984,14 +6047,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559989504"/>
+        <c:crossAx val="492175744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559989504"/>
+        <c:axId val="492175744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6042,12 +6105,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524069888"/>
+        <c:crossAx val="485812864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="559991424"/>
+        <c:axId val="492177280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6084,12 +6147,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="605799168"/>
+        <c:crossAx val="492178816"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="605799168"/>
+        <c:axId val="492178816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6098,7 +6161,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="559991424"/>
+        <c:crossAx val="492177280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6248,7 +6311,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6428,6 +6491,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6437,7 +6503,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6616,6 +6682,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6659,7 +6728,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6839,6 +6908,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6848,7 +6920,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7028,6 +7100,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17567754.333578344</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17963358.223627001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7070,7 +7145,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7250,6 +7325,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7259,7 +7337,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7439,6 +7517,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7604968.9543284345</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8000572.8443770912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7460,11 +7541,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99914880"/>
-        <c:axId val="99916416"/>
+        <c:axId val="494512768"/>
+        <c:axId val="501473664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99914880"/>
+        <c:axId val="494512768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7507,14 +7588,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99916416"/>
+        <c:crossAx val="501473664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="99916416"/>
+        <c:axId val="501473664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7565,7 +7646,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99914880"/>
+        <c:crossAx val="494512768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7726,7 +7807,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7906,6 +7987,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-394977.32401696721</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7920,8 +8004,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="399443840"/>
-        <c:axId val="399442304"/>
+        <c:axId val="501894144"/>
+        <c:axId val="501892608"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7946,7 +8030,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8126,6 +8210,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8135,7 +8222,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8315,6 +8402,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8331,11 +8421,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="374875264"/>
-        <c:axId val="374876800"/>
+        <c:axId val="501889280"/>
+        <c:axId val="501891072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="374875264"/>
+        <c:axId val="501889280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8378,14 +8468,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="374876800"/>
+        <c:crossAx val="501891072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="374876800"/>
+        <c:axId val="501891072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8436,12 +8526,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="374875264"/>
+        <c:crossAx val="501889280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399442304"/>
+        <c:axId val="501892608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8478,12 +8568,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399443840"/>
+        <c:crossAx val="501894144"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="399443840"/>
+        <c:axId val="501894144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8492,7 +8582,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399442304"/>
+        <c:crossAx val="501892608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8642,7 +8732,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8822,6 +8912,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8831,7 +8924,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9010,6 +9103,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9053,7 +9149,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9233,6 +9329,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9242,7 +9341,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9422,6 +9521,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>157278204.92011258</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>160901580.29612678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9464,7 +9566,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9644,6 +9746,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9653,7 +9758,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9833,6 +9938,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>69838252.257509872</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>73461627.633524075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9854,11 +9962,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399463168"/>
-        <c:axId val="399464704"/>
+        <c:axId val="501934336"/>
+        <c:axId val="501936128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399463168"/>
+        <c:axId val="501934336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9901,14 +10009,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399464704"/>
+        <c:crossAx val="501936128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399464704"/>
+        <c:axId val="501936128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9959,7 +10067,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399463168"/>
+        <c:crossAx val="501934336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10120,7 +10228,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10300,6 +10408,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>116883008.32632542</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>105957807.12580833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10314,8 +10425,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="399484032"/>
-        <c:axId val="399482240"/>
+        <c:axId val="501959296"/>
+        <c:axId val="501957760"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10340,7 +10451,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10520,6 +10631,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10529,7 +10643,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10709,6 +10823,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10725,11 +10842,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399479168"/>
-        <c:axId val="399480704"/>
+        <c:axId val="501950336"/>
+        <c:axId val="501951872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399479168"/>
+        <c:axId val="501950336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10772,14 +10889,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399480704"/>
+        <c:crossAx val="501951872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399480704"/>
+        <c:axId val="501951872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10830,12 +10947,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399479168"/>
+        <c:crossAx val="501950336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399482240"/>
+        <c:axId val="501957760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10872,12 +10989,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399484032"/>
+        <c:crossAx val="501959296"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="399484032"/>
+        <c:axId val="501959296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10886,7 +11003,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399482240"/>
+        <c:crossAx val="501957760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11036,7 +11153,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11216,6 +11333,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11225,7 +11345,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11404,6 +11524,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11447,7 +11570,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11627,6 +11750,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11636,7 +11762,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11816,6 +11942,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>162688850.00592482</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>166564935.16431901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11858,7 +11987,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12038,6 +12167,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12047,7 +12179,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12227,6 +12359,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>79107853.670304805</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>82983938.828698993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12248,11 +12383,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401916288"/>
-        <c:axId val="401917824"/>
+        <c:axId val="502028160"/>
+        <c:axId val="502029696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401916288"/>
+        <c:axId val="502028160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12295,14 +12430,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401917824"/>
+        <c:crossAx val="502029696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401917824"/>
+        <c:axId val="502029696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12353,7 +12488,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401916288"/>
+        <c:crossAx val="502028160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13067,7 +13202,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15710,6 +15845,44 @@
         <v>1556201.7813372496</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="15">
+        <v>11261973.499519134</v>
+      </c>
+      <c r="H63" s="15">
+        <v>14370278.443152532</v>
+      </c>
+      <c r="I63" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J63" s="15">
+        <v>16842108.331714839</v>
+      </c>
+      <c r="K63" s="15">
+        <v>7480773.5139874145</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2471829.8885623058</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15726,7 +15899,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19823,6 +19996,71 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:21" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-1098753.7286700674</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-861092.24840221775</v>
+      </c>
+      <c r="G63" s="15">
+        <v>11950111.458020555</v>
+      </c>
+      <c r="H63" s="15">
+        <v>15248342.493950574</v>
+      </c>
+      <c r="I63" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J63" s="15">
+        <v>18094777.250086345</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8087003.7105634734</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2846434.7561357729</v>
+      </c>
+      <c r="M63" s="23">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="N63" s="23">
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="O63" s="23">
+        <v>1.2480000257492065</v>
+      </c>
+      <c r="P63" s="23">
+        <v>1.0304285770370849</v>
+      </c>
+      <c r="Q63" s="23">
+        <v>0.21757144871212164</v>
+      </c>
+      <c r="R63" s="23">
+        <v>0.10519728409189744</v>
+      </c>
+      <c r="S63" s="9">
+        <v>1.5779592613784615E-3</v>
+      </c>
+      <c r="T63" s="9">
+        <v>137.88153727242442</v>
+      </c>
+      <c r="U63" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19839,7 +20077,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22831,6 +23069,50 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="15">
+        <v>12043831.475181028</v>
+      </c>
+      <c r="H63" s="15">
+        <v>15367929.237992419</v>
+      </c>
+      <c r="I63" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J63" s="15">
+        <v>17963358.223627001</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8000572.8443770912</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2595428.9856345826</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -22847,7 +23129,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25839,6 +26121,50 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-13940556.981917825</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-10925201.200517096</v>
+      </c>
+      <c r="G63" s="15">
+        <v>105957807.12580833</v>
+      </c>
+      <c r="H63" s="15">
+        <v>135202164.31771317</v>
+      </c>
+      <c r="I63" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J63" s="15">
+        <v>160901580.29612678</v>
+      </c>
+      <c r="K63" s="15">
+        <v>73461627.633524075</v>
+      </c>
+      <c r="L63" s="14">
+        <v>25699415.978413627</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -25855,7 +26181,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AI63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -29215,6 +29541,56 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="63" spans="1:16" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="14">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="14">
+        <v>-10715332.987082755</v>
+      </c>
+      <c r="H63" s="15">
+        <v>-8397596.2342296485</v>
+      </c>
+      <c r="I63" s="15">
+        <v>116637335.79108463</v>
+      </c>
+      <c r="J63" s="15">
+        <v>148829243.13904074</v>
+      </c>
+      <c r="K63" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L63" s="15">
+        <v>166564935.16431901</v>
+      </c>
+      <c r="M63" s="15">
+        <v>82983938.828698993</v>
+      </c>
+      <c r="N63" s="14">
+        <v>17735692.025278274</v>
+      </c>
+      <c r="O63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="P63" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -745,6 +745,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -754,7 +757,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -936,6 +939,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -979,7 +985,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1162,6 +1168,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1171,7 +1180,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1354,6 +1363,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>16842108.331714839</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>14938834.477348203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1396,7 +1408,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1579,6 +1591,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1588,7 +1603,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1771,6 +1786,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>7480773.5139874145</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5577499.6596207786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1792,11 +1810,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494486656"/>
-        <c:axId val="494488960"/>
+        <c:axId val="541882240"/>
+        <c:axId val="541883776"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494486656"/>
+        <c:axId val="541882240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1839,14 +1857,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494488960"/>
+        <c:crossAx val="541883776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494488960"/>
+        <c:axId val="541883776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1897,7 +1915,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494486656"/>
+        <c:crossAx val="541882240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2058,7 +2076,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2241,6 +2259,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-10715332.987082755</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-3137492.7659313167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2255,8 +2276,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="502073984"/>
-        <c:axId val="502072448"/>
+        <c:axId val="548474240"/>
+        <c:axId val="548472704"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2281,7 +2302,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2464,6 +2485,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2473,7 +2497,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2656,6 +2680,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2672,11 +2699,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502065024"/>
-        <c:axId val="502066560"/>
+        <c:axId val="547674752"/>
+        <c:axId val="548471168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502065024"/>
+        <c:axId val="547674752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2719,14 +2746,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502066560"/>
+        <c:crossAx val="548471168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502066560"/>
+        <c:axId val="548471168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2777,12 +2804,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502065024"/>
+        <c:crossAx val="547674752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="502072448"/>
+        <c:axId val="548472704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2819,12 +2846,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502073984"/>
+        <c:crossAx val="548474240"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="502073984"/>
+        <c:axId val="548474240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2833,7 +2860,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="502072448"/>
+        <c:crossAx val="548472704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2965,7 +2992,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3148,6 +3175,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-915628.10722505616</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3162,8 +3192,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="620203008"/>
-        <c:axId val="620200704"/>
+        <c:axId val="554103936"/>
+        <c:axId val="554102144"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3188,7 +3218,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3371,6 +3401,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3380,7 +3413,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3563,6 +3596,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3579,11 +3615,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="515625344"/>
-        <c:axId val="515626880"/>
+        <c:axId val="554061184"/>
+        <c:axId val="554100608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="515625344"/>
+        <c:axId val="554061184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3626,14 +3662,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="515626880"/>
+        <c:crossAx val="554100608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="515626880"/>
+        <c:axId val="554100608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3684,12 +3720,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="515625344"/>
+        <c:crossAx val="554061184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="620200704"/>
+        <c:axId val="554102144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3726,12 +3762,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620203008"/>
+        <c:crossAx val="554103936"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="620203008"/>
+        <c:axId val="554103936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3740,7 +3776,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="620200704"/>
+        <c:crossAx val="554102144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3890,7 +3926,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4073,6 +4109,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4082,7 +4121,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4264,6 +4303,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4307,7 +4349,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4490,6 +4532,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4499,7 +4544,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4682,6 +4727,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>18094777.250086345</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16075208.060388925</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4724,7 +4772,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4907,6 +4955,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4916,7 +4967,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5099,6 +5150,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8087003.7105634734</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6067434.5208660532</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5120,11 +5174,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="485796864"/>
-        <c:axId val="485798656"/>
+        <c:axId val="567122944"/>
+        <c:axId val="676455168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="485796864"/>
+        <c:axId val="567122944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5167,14 +5221,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="485798656"/>
+        <c:crossAx val="676455168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="485798656"/>
+        <c:axId val="676455168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5225,7 +5279,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="485796864"/>
+        <c:crossAx val="567122944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5386,7 +5440,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5569,6 +5623,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-1098753.7286700674</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5583,8 +5640,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="492178816"/>
-        <c:axId val="492177280"/>
+        <c:axId val="90252032"/>
+        <c:axId val="90250240"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5609,7 +5666,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5792,6 +5849,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5801,7 +5861,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5984,6 +6044,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6000,11 +6063,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="485812864"/>
-        <c:axId val="492175744"/>
+        <c:axId val="90247168"/>
+        <c:axId val="90248704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="485812864"/>
+        <c:axId val="90247168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6047,14 +6110,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492175744"/>
+        <c:crossAx val="90248704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="492175744"/>
+        <c:axId val="90248704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6105,12 +6168,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="485812864"/>
+        <c:crossAx val="90247168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="492177280"/>
+        <c:axId val="90250240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6147,12 +6210,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492178816"/>
+        <c:crossAx val="90252032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="492178816"/>
+        <c:axId val="90252032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6161,7 +6224,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="492177280"/>
+        <c:crossAx val="90250240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6311,7 +6374,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6494,6 +6557,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6503,7 +6569,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6685,6 +6751,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6728,7 +6797,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6911,6 +6980,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6920,7 +6992,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7103,6 +7175,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>17963358.223627001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>15927950.34825873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7145,7 +7220,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7328,6 +7403,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7337,7 +7415,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7520,6 +7598,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8000572.8443770912</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5965164.9690088201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7541,11 +7622,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494512768"/>
-        <c:axId val="501473664"/>
+        <c:axId val="103890944"/>
+        <c:axId val="103892480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494512768"/>
+        <c:axId val="103890944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7588,14 +7669,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501473664"/>
+        <c:crossAx val="103892480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501473664"/>
+        <c:axId val="103892480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7646,7 +7727,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494512768"/>
+        <c:crossAx val="103890944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7807,7 +7888,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7990,6 +8071,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-915628.10722505616</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8004,8 +8088,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="501894144"/>
-        <c:axId val="501892608"/>
+        <c:axId val="103916288"/>
+        <c:axId val="103914496"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8030,7 +8114,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8213,6 +8297,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8222,7 +8309,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8405,6 +8492,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8421,11 +8511,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501889280"/>
-        <c:axId val="501891072"/>
+        <c:axId val="103911424"/>
+        <c:axId val="103912960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501889280"/>
+        <c:axId val="103911424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8468,14 +8558,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501891072"/>
+        <c:crossAx val="103912960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501891072"/>
+        <c:axId val="103912960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8526,12 +8616,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501889280"/>
+        <c:crossAx val="103911424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="501892608"/>
+        <c:axId val="103914496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8568,12 +8658,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501894144"/>
+        <c:crossAx val="103916288"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="501894144"/>
+        <c:axId val="103916288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8582,7 +8672,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="501892608"/>
+        <c:crossAx val="103914496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8732,7 +8822,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8915,6 +9005,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8924,7 +9017,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9106,6 +9199,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9149,7 +9245,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9332,6 +9428,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9341,7 +9440,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9524,6 +9623,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>160901580.29612678</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>142994707.75933877</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9566,7 +9668,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9749,6 +9851,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9758,7 +9863,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9941,6 +10046,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>73461627.633524075</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>55554755.096736059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9962,11 +10070,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501934336"/>
-        <c:axId val="501936128"/>
+        <c:axId val="167198720"/>
+        <c:axId val="167200256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501934336"/>
+        <c:axId val="167198720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10009,14 +10117,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501936128"/>
+        <c:crossAx val="167200256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501936128"/>
+        <c:axId val="167200256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10067,7 +10175,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501934336"/>
+        <c:crossAx val="167198720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10228,7 +10336,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10411,6 +10519,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>105957807.12580833</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>103421867.6557951</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10425,8 +10536,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="501959296"/>
-        <c:axId val="501957760"/>
+        <c:axId val="167235584"/>
+        <c:axId val="167233792"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10451,7 +10562,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10634,6 +10745,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10643,7 +10757,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10826,6 +10940,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10842,11 +10959,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="501950336"/>
-        <c:axId val="501951872"/>
+        <c:axId val="167230464"/>
+        <c:axId val="167232256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="501950336"/>
+        <c:axId val="167230464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10889,14 +11006,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501951872"/>
+        <c:crossAx val="167232256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="501951872"/>
+        <c:axId val="167232256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10947,12 +11064,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501950336"/>
+        <c:crossAx val="167230464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="501957760"/>
+        <c:axId val="167233792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10989,12 +11106,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="501959296"/>
+        <c:crossAx val="167235584"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="501959296"/>
+        <c:axId val="167235584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11003,7 +11120,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="501957760"/>
+        <c:crossAx val="167233792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11153,7 +11270,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11336,6 +11453,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11345,7 +11465,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11527,6 +11647,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11570,7 +11693,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11753,6 +11876,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11762,7 +11888,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11945,6 +12071,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>166564935.16431901</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>146853221.96737075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11987,7 +12116,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12170,6 +12299,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12179,7 +12311,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12362,6 +12494,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>82983938.828698993</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>63272225.631750733</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12383,11 +12518,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502028160"/>
-        <c:axId val="502029696"/>
+        <c:axId val="169995264"/>
+        <c:axId val="373633792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502028160"/>
+        <c:axId val="169995264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12430,14 +12565,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502029696"/>
+        <c:crossAx val="373633792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502029696"/>
+        <c:axId val="373633792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12488,7 +12623,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502028160"/>
+        <c:crossAx val="169995264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13202,7 +13337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15883,6 +16018,44 @@
         <v>2471829.8885623058</v>
       </c>
     </row>
+    <row r="64" spans="1:12" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>10977805.121812543</v>
+      </c>
+      <c r="H64" s="15">
+        <v>12152430.19656173</v>
+      </c>
+      <c r="I64" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J64" s="15">
+        <v>14938834.477348203</v>
+      </c>
+      <c r="K64" s="15">
+        <v>5577499.6596207786</v>
+      </c>
+      <c r="L64" s="14">
+        <v>2786404.2807864728</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15899,7 +16072,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20061,6 +20234,71 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="64" spans="1:21" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>11665943.080313964</v>
+      </c>
+      <c r="H64" s="15">
+        <v>12914198.912028985</v>
+      </c>
+      <c r="I64" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J64" s="15">
+        <v>16075208.060388925</v>
+      </c>
+      <c r="K64" s="15">
+        <v>6067434.5208660532</v>
+      </c>
+      <c r="L64" s="14">
+        <v>3161009.1483599399</v>
+      </c>
+      <c r="M64" s="23">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="N64" s="23">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="O64" s="23">
+        <v>1.1546666622161865</v>
+      </c>
+      <c r="P64" s="23">
+        <v>1.0564761956532798</v>
+      </c>
+      <c r="Q64" s="23">
+        <v>9.8190466562906753E-2</v>
+      </c>
+      <c r="R64" s="23">
+        <v>8.5721089726402591E-2</v>
+      </c>
+      <c r="S64" s="9">
+        <v>1.2858163458960388E-3</v>
+      </c>
+      <c r="T64" s="9">
+        <v>76.364301073246494</v>
+      </c>
+      <c r="U64" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20077,7 +20315,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23113,6 +23351,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>11759663.097474437</v>
+      </c>
+      <c r="H64" s="15">
+        <v>13017946.970399981</v>
+      </c>
+      <c r="I64" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J64" s="15">
+        <v>15927950.34825873</v>
+      </c>
+      <c r="K64" s="15">
+        <v>5965164.9690088201</v>
+      </c>
+      <c r="L64" s="14">
+        <v>2910003.3778587496</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23129,7 +23411,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26165,6 +26447,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-2807284.9763754238</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-2535939.4700132306</v>
+      </c>
+      <c r="G64" s="15">
+        <v>103421867.6557951</v>
+      </c>
+      <c r="H64" s="15">
+        <v>114488006.80454972</v>
+      </c>
+      <c r="I64" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J64" s="15">
+        <v>142994707.75933877</v>
+      </c>
+      <c r="K64" s="15">
+        <v>55554755.096736059</v>
+      </c>
+      <c r="L64" s="14">
+        <v>28506700.95478905</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -26181,7 +26507,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -29591,6 +29917,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:16" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>4485200</v>
+      </c>
+      <c r="F64" s="14">
+        <v>4013151.7473958335</v>
+      </c>
+      <c r="G64" s="14">
+        <v>-3137492.7659313167</v>
+      </c>
+      <c r="H64" s="15">
+        <v>-2834230.1579510788</v>
+      </c>
+      <c r="I64" s="15">
+        <v>113803105.63313356</v>
+      </c>
+      <c r="J64" s="15">
+        <v>125980037.17616116</v>
+      </c>
+      <c r="K64" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L64" s="15">
+        <v>146853221.96737075</v>
+      </c>
+      <c r="M64" s="15">
+        <v>63272225.631750733</v>
+      </c>
+      <c r="N64" s="14">
+        <v>20873184.79120959</v>
+      </c>
+      <c r="O64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="P64" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -748,6 +748,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -757,7 +760,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -942,6 +945,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -985,7 +991,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1171,6 +1177,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1180,7 +1189,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1366,6 +1375,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>14938834.477348203</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15015678.778184865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1408,7 +1420,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1594,6 +1606,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1603,7 +1618,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1789,6 +1804,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5577499.6596207786</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5654343.9604574405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1810,11 +1828,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="541882240"/>
-        <c:axId val="541883776"/>
+        <c:axId val="421941632"/>
+        <c:axId val="421943168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="541882240"/>
+        <c:axId val="421941632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1857,14 +1875,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541883776"/>
+        <c:crossAx val="421943168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="541883776"/>
+        <c:axId val="421943168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1915,7 +1933,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541882240"/>
+        <c:crossAx val="421941632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2076,7 +2094,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2262,6 +2280,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-3137492.7659313167</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-1153306.5826965235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2276,8 +2297,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="548474240"/>
-        <c:axId val="548472704"/>
+        <c:axId val="424905728"/>
+        <c:axId val="424904192"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2302,7 +2323,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2488,6 +2509,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2497,7 +2521,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2683,6 +2707,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2699,11 +2726,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547674752"/>
-        <c:axId val="548471168"/>
+        <c:axId val="424900864"/>
+        <c:axId val="424902656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547674752"/>
+        <c:axId val="424900864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2746,14 +2773,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548471168"/>
+        <c:crossAx val="424902656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="548471168"/>
+        <c:axId val="424902656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2804,12 +2831,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547674752"/>
+        <c:crossAx val="424900864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="548472704"/>
+        <c:axId val="424904192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2846,12 +2873,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548474240"/>
+        <c:crossAx val="424905728"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="548474240"/>
+        <c:axId val="424905728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2860,7 +2887,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="548472704"/>
+        <c:crossAx val="424904192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2992,7 +3019,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3178,6 +3205,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3192,8 +3222,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="554103936"/>
-        <c:axId val="554102144"/>
+        <c:axId val="489280256"/>
+        <c:axId val="485510144"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3218,7 +3248,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3404,6 +3434,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3413,7 +3446,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3599,6 +3632,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3615,11 +3651,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="554061184"/>
-        <c:axId val="554100608"/>
+        <c:axId val="429223296"/>
+        <c:axId val="485508224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="554061184"/>
+        <c:axId val="429223296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3662,14 +3698,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="554100608"/>
+        <c:crossAx val="485508224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="554100608"/>
+        <c:axId val="485508224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3720,12 +3756,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="554061184"/>
+        <c:crossAx val="429223296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="554102144"/>
+        <c:axId val="485510144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3762,12 +3798,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="554103936"/>
+        <c:crossAx val="489280256"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="554103936"/>
+        <c:axId val="489280256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3776,7 +3812,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="554102144"/>
+        <c:crossAx val="485510144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3926,7 +3962,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4112,6 +4148,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4121,7 +4160,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4306,6 +4345,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4349,7 +4391,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4535,6 +4577,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4544,7 +4589,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4730,6 +4775,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>16075208.060388925</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16156869.305934794</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4772,7 +4820,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4958,6 +5006,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4967,7 +5018,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5153,6 +5204,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6067434.5208660532</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6149095.7664119229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5174,11 +5228,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="567122944"/>
-        <c:axId val="676455168"/>
+        <c:axId val="159211520"/>
+        <c:axId val="159213056"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="567122944"/>
+        <c:axId val="159211520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5221,14 +5275,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676455168"/>
+        <c:crossAx val="159213056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="676455168"/>
+        <c:axId val="159213056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5279,7 +5333,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567122944"/>
+        <c:crossAx val="159211520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5440,7 +5494,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5626,6 +5680,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5640,8 +5697,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="90252032"/>
-        <c:axId val="90250240"/>
+        <c:axId val="159245056"/>
+        <c:axId val="159239168"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5666,7 +5723,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5852,6 +5909,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5861,7 +5921,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6047,6 +6107,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6063,11 +6126,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90247168"/>
-        <c:axId val="90248704"/>
+        <c:axId val="159236096"/>
+        <c:axId val="159237632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90247168"/>
+        <c:axId val="159236096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6110,14 +6173,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90248704"/>
+        <c:crossAx val="159237632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90248704"/>
+        <c:axId val="159237632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6168,12 +6231,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90247168"/>
+        <c:crossAx val="159236096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="90250240"/>
+        <c:axId val="159239168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6210,12 +6273,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90252032"/>
+        <c:crossAx val="159245056"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="90252032"/>
+        <c:axId val="159245056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6224,7 +6287,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="90250240"/>
+        <c:crossAx val="159239168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6374,7 +6437,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6560,6 +6623,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6569,7 +6635,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6754,6 +6820,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6797,7 +6866,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6983,6 +7052,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6992,7 +7064,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7178,6 +7250,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>15927950.34825873</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16010267.631064614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7220,7 +7295,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7406,6 +7481,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7415,7 +7493,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7601,6 +7679,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5965164.9690088201</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6047482.2518147044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7622,11 +7703,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="103890944"/>
-        <c:axId val="103892480"/>
+        <c:axId val="160088064"/>
+        <c:axId val="160089600"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="103890944"/>
+        <c:axId val="160088064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7669,14 +7750,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103892480"/>
+        <c:crossAx val="160089600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103892480"/>
+        <c:axId val="160089600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7727,7 +7808,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103890944"/>
+        <c:crossAx val="160088064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7888,7 +7969,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8074,6 +8155,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8088,8 +8172,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="103916288"/>
-        <c:axId val="103914496"/>
+        <c:axId val="392810880"/>
+        <c:axId val="392784512"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8114,7 +8198,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8300,6 +8384,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8309,7 +8396,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8495,6 +8582,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8511,11 +8601,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="103911424"/>
-        <c:axId val="103912960"/>
+        <c:axId val="392760704"/>
+        <c:axId val="392782976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="103911424"/>
+        <c:axId val="392760704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8558,14 +8648,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103912960"/>
+        <c:crossAx val="392782976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103912960"/>
+        <c:axId val="392782976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8616,12 +8706,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103911424"/>
+        <c:crossAx val="392760704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="103914496"/>
+        <c:axId val="392784512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8658,12 +8748,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103916288"/>
+        <c:crossAx val="392810880"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="103916288"/>
+        <c:axId val="392810880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8672,7 +8762,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103914496"/>
+        <c:crossAx val="392784512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8822,7 +8912,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9008,6 +9098,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9017,7 +9110,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9202,6 +9295,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9245,7 +9341,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9431,6 +9527,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9440,7 +9539,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9626,6 +9725,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>142994707.75933877</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>143718657.6767444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9668,7 +9770,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9854,6 +9956,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9863,7 +9968,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10049,6 +10154,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>55554755.096736059</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>56278705.014141694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10070,11 +10178,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="167198720"/>
-        <c:axId val="167200256"/>
+        <c:axId val="421969280"/>
+        <c:axId val="421971072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="167198720"/>
+        <c:axId val="421969280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10117,14 +10225,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167200256"/>
+        <c:crossAx val="421971072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="167200256"/>
+        <c:axId val="421971072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10175,7 +10283,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167198720"/>
+        <c:crossAx val="421969280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10336,7 +10444,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10522,6 +10630,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>103421867.6557951</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>100966483.27033739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10536,8 +10647,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="167235584"/>
-        <c:axId val="167233792"/>
+        <c:axId val="422927744"/>
+        <c:axId val="422926208"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10562,7 +10673,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10748,6 +10859,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10757,7 +10871,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10943,6 +11057,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10959,11 +11076,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="167230464"/>
-        <c:axId val="167232256"/>
+        <c:axId val="422652544"/>
+        <c:axId val="422924672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="167230464"/>
+        <c:axId val="422652544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11006,14 +11123,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167232256"/>
+        <c:crossAx val="422924672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="167232256"/>
+        <c:axId val="422924672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11064,12 +11181,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167230464"/>
+        <c:crossAx val="422652544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="167233792"/>
+        <c:axId val="422926208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11106,12 +11223,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167235584"/>
+        <c:crossAx val="422927744"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="167235584"/>
+        <c:axId val="422927744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11120,7 +11237,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="167233792"/>
+        <c:crossAx val="422926208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11270,7 +11387,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11456,6 +11573,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11465,7 +11585,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11650,6 +11770,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11693,7 +11816,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11879,6 +12002,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11888,7 +12014,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12074,6 +12200,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>146853221.96737075</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>147649840.2338075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12116,7 +12245,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12302,6 +12431,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12311,7 +12443,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12497,6 +12629,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>63272225.631750733</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>64068843.898187488</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12518,11 +12653,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="169995264"/>
-        <c:axId val="373633792"/>
+        <c:axId val="424802944"/>
+        <c:axId val="424870272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="169995264"/>
+        <c:axId val="424802944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12565,14 +12700,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="373633792"/>
+        <c:crossAx val="424870272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="373633792"/>
+        <c:axId val="424870272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12623,7 +12758,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="169995264"/>
+        <c:crossAx val="424802944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13337,7 +13472,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16056,6 +16191,44 @@
         <v>2786404.2807864728</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>10700270.628994567</v>
+      </c>
+      <c r="H65" s="15">
+        <v>11920101.082721591</v>
+      </c>
+      <c r="I65" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J65" s="15">
+        <v>15015678.778184865</v>
+      </c>
+      <c r="K65" s="15">
+        <v>5654343.9604574405</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3095577.6954632737</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -16072,7 +16245,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20299,6 +20472,71 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:21" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>11388408.587495988</v>
+      </c>
+      <c r="H65" s="15">
+        <v>12686686.742898053</v>
+      </c>
+      <c r="I65" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J65" s="15">
+        <v>16156869.305934794</v>
+      </c>
+      <c r="K65" s="15">
+        <v>6149095.7664119229</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3470182.5630367408</v>
+      </c>
+      <c r="M65" s="23">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="N65" s="23">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="O65" s="23">
+        <v>1.1276666720708211</v>
+      </c>
+      <c r="P65" s="23">
+        <v>1.0799047677289875</v>
+      </c>
+      <c r="Q65" s="23">
+        <v>4.7761904341833583E-2</v>
+      </c>
+      <c r="R65" s="23">
+        <v>7.0020411087542242E-2</v>
+      </c>
+      <c r="S65" s="9">
+        <v>1.0503061663131336E-3</v>
+      </c>
+      <c r="T65" s="9">
+        <v>45.47426824074654</v>
+      </c>
+      <c r="U65" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20315,7 +20553,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23395,6 +23633,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>11482128.604656462</v>
+      </c>
+      <c r="H65" s="15">
+        <v>12791090.838529063</v>
+      </c>
+      <c r="I65" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J65" s="15">
+        <v>16010267.631064614</v>
+      </c>
+      <c r="K65" s="15">
+        <v>6047482.2518147044</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3219176.7925355504</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23411,7 +23693,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26491,6 +26773,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-2735298.1140760505</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-2455384.385457715</v>
+      </c>
+      <c r="G65" s="15">
+        <v>100966483.27033739</v>
+      </c>
+      <c r="H65" s="15">
+        <v>112476658.60787931</v>
+      </c>
+      <c r="I65" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J65" s="15">
+        <v>143718657.6767444</v>
+      </c>
+      <c r="K65" s="15">
+        <v>56278705.014141694</v>
+      </c>
+      <c r="L65" s="14">
+        <v>31241999.068865102</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -26507,7 +26833,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI64"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -29967,6 +30293,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:16" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="14">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="14">
+        <v>-1153306.5826965235</v>
+      </c>
+      <c r="H65" s="15">
+        <v>-1035284.2201096574</v>
+      </c>
+      <c r="I65" s="15">
+        <v>112767821.4130239</v>
+      </c>
+      <c r="J65" s="15">
+        <v>125623348.8599014</v>
+      </c>
+      <c r="K65" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L65" s="15">
+        <v>147649840.2338075</v>
+      </c>
+      <c r="M65" s="15">
+        <v>64068843.898187488</v>
+      </c>
+      <c r="N65" s="14">
+        <v>22026491.373906113</v>
+      </c>
+      <c r="O65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="P65" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">
